--- a/output/エラー一覧.xlsx
+++ b/output/エラー一覧.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$F$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -447,12 +447,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
@@ -503,7 +503,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2026年4月</t>
+          <t>2026年9月</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>2026年4月</t>
+          <t>2026年8月</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr"/>
@@ -559,12 +559,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2026年4月</t>
+          <t>2026年12月</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -573,45 +573,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>遡及支給等の可能性があるため、自治体の算定ルールと元データを確認してください</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>U002</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>佐藤 花子</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>2026年4月</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>対象月と支給月が異なります</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>遡及支給等の可能性があるため、自治体の算定ルールと元データを確認してください</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:F4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>